--- a/nseIndia/exportedData/MarketStatistics.xlsx
+++ b/nseIndia/exportedData/MarketStatistics.xlsx
@@ -457,20 +457,20 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2806</v>
+        <v>3084</v>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n">
-        <v>1183</v>
+        <v>1319</v>
       </c>
       <c r="D2" t="n">
-        <v>1528</v>
+        <v>1668</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14-Aug-2025 12:03:27</t>
+          <t>29-Aug-2025 16:00:29</t>
         </is>
       </c>
     </row>
